--- a/Roadmap + Aims per day/Затраченное время и изученное.xlsx
+++ b/Roadmap + Aims per day/Затраченное время и изученное.xlsx
@@ -1,20 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java\Conspects\Roadmap + Aims per day\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24456" windowHeight="9576"/>
+    <workbookView windowWidth="24460" windowHeight="9720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="67">
   <si>
     <t>8+ часов</t>
   </si>
@@ -230,16 +225,23 @@
   </si>
   <si>
     <t>Решал задачу 3531, но система LeetCode так и не приняла ее. Memory Limit Excedeed 622/634 тесткейсов пройдено.</t>
+  </si>
+  <si>
+    <t>Разобрал урок 17 и половину 18</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd\-mmm"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="dd\-mmm"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,8 +256,152 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -276,19 +422,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -300,24 +446,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -325,26 +651,269 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -360,25 +929,64 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -636,24 +1244,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F54"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="6.5546875" customWidth="1"/>
     <col min="3" max="3" width="14.109375" customWidth="1"/>
-    <col min="4" max="4" width="6.77734375" customWidth="1"/>
+    <col min="4" max="4" width="6.78125" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="243.44140625" customWidth="1"/>
+    <col min="6" max="6" width="243.4453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1">
+    <row r="1" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -661,12 +1269,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1">
+    <row r="2" customHeight="1" spans="1:1">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1">
+    <row r="3" customHeight="1" spans="1:6">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -683,7 +1291,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1">
+    <row r="4" customHeight="1" spans="1:6">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
@@ -693,14 +1301,14 @@
       <c r="D4" s="5">
         <v>45908</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="16" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1">
+    <row r="5" customHeight="1" spans="1:6">
       <c r="A5" s="6" t="s">
         <v>11</v>
       </c>
@@ -710,266 +1318,266 @@
       <c r="D5" s="7">
         <v>45909</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="17">
         <v>5</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="18" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1">
+    <row r="6" customHeight="1" spans="3:6">
       <c r="C6" s="3">
         <v>3</v>
       </c>
       <c r="D6" s="7">
         <v>45912</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1">
+    <row r="7" customHeight="1" spans="3:6">
       <c r="C7" s="6">
         <v>4</v>
       </c>
       <c r="D7" s="8">
         <v>45913</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="20" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1">
+    <row r="8" customHeight="1" spans="3:6">
       <c r="C8" s="6">
         <v>5</v>
       </c>
       <c r="D8" s="8">
         <v>45915</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1">
+    <row r="9" customHeight="1" spans="3:6">
       <c r="C9" s="6">
         <v>6</v>
       </c>
       <c r="D9" s="8">
         <v>45916</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1">
+    <row r="10" customHeight="1" spans="3:6">
       <c r="C10" s="3">
         <v>7</v>
       </c>
       <c r="D10" s="7">
         <v>45917</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="22" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" customHeight="1">
+    <row r="11" customHeight="1" spans="3:6">
       <c r="C11" s="3">
         <v>8</v>
       </c>
       <c r="D11" s="7">
         <v>45918</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="23" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15" customHeight="1">
+    <row r="12" customHeight="1" spans="3:6">
       <c r="C12" s="6">
         <v>9</v>
       </c>
       <c r="D12" s="8">
         <v>45919</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="19" t="s">
         <v>23</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1">
+    <row r="13" customHeight="1" spans="3:6">
       <c r="C13" s="4">
         <v>10</v>
       </c>
       <c r="D13" s="5">
         <v>45920</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="F13" s="24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15" customHeight="1">
+    <row r="14" customHeight="1" spans="3:6">
       <c r="C14" s="6">
         <v>11</v>
       </c>
       <c r="D14" s="8">
         <v>45921</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="21" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1">
+    <row r="15" customHeight="1" spans="3:6">
       <c r="C15" s="6">
         <v>12</v>
       </c>
       <c r="D15" s="8">
         <v>45923</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="F15" s="21" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1">
+    <row r="16" customHeight="1" spans="3:6">
       <c r="C16" s="6">
         <v>13</v>
       </c>
       <c r="D16" s="8">
         <v>45925</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="21" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="3:6" ht="15" customHeight="1">
+    <row r="17" customHeight="1" spans="3:6">
       <c r="C17" s="4">
         <v>14</v>
       </c>
       <c r="D17" s="5">
         <v>45927</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F17" s="23" t="s">
+      <c r="F17" s="24" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="3:6" ht="15" customHeight="1">
+    <row r="18" customHeight="1" spans="3:6">
       <c r="C18" s="4">
         <v>15</v>
       </c>
       <c r="D18" s="5">
         <v>45929</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="23" t="s">
+      <c r="F18" s="24" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="3:6" ht="15" customHeight="1">
+    <row r="19" customHeight="1" spans="3:6">
       <c r="C19" s="3">
         <v>16</v>
       </c>
       <c r="D19" s="7">
         <v>45930</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="F19" s="22" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="3:6" ht="15" customHeight="1">
+    <row r="20" customHeight="1" spans="3:6">
       <c r="C20" s="6">
         <v>17</v>
       </c>
       <c r="D20" s="8">
         <v>45931</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="F20" s="21" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="3:6" ht="15" customHeight="1">
+    <row r="21" customHeight="1" spans="3:6">
       <c r="C21" s="6">
         <v>18</v>
       </c>
       <c r="D21" s="8">
         <v>45932</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="20" t="s">
+      <c r="F21" s="21" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="3:6" ht="15" customHeight="1">
+    <row r="22" customHeight="1" spans="3:6">
       <c r="C22" s="4">
         <v>19</v>
       </c>
       <c r="D22" s="5">
         <v>45934</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="23" t="s">
+      <c r="F22" s="24" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="3:6" ht="15" customHeight="1">
+    <row r="23" customHeight="1" spans="3:6">
       <c r="C23" s="3">
         <v>20</v>
       </c>
       <c r="D23" s="7">
         <v>45935</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="3:6" ht="15" customHeight="1">
+    <row r="24" customHeight="1" spans="3:6">
       <c r="C24" s="2">
         <v>21</v>
       </c>
@@ -983,35 +1591,35 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="3:6" ht="15" customHeight="1">
+    <row r="25" customHeight="1" spans="3:6">
       <c r="C25" s="3">
         <v>22</v>
       </c>
       <c r="D25" s="7">
         <v>45937</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="E25" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="3:6" ht="15" customHeight="1">
+    <row r="26" customHeight="1" spans="3:6">
       <c r="C26" s="3">
         <v>23</v>
       </c>
       <c r="D26" s="7">
         <v>45938</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="3:6" ht="15" customHeight="1">
+    <row r="27" customHeight="1" spans="3:6">
       <c r="C27" s="2">
         <v>24</v>
       </c>
@@ -1025,7 +1633,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="3:6" ht="15" customHeight="1">
+    <row r="28" customHeight="1" spans="3:6">
       <c r="C28" s="10"/>
       <c r="D28" s="11">
         <v>45940</v>
@@ -1037,49 +1645,49 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="3:6" ht="15" customHeight="1">
+    <row r="29" customHeight="1" spans="3:6">
       <c r="C29" s="3">
         <v>25</v>
       </c>
       <c r="D29" s="7">
         <v>45941</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E29" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="3:6" ht="15" customHeight="1">
+    <row r="30" customHeight="1" spans="3:6">
       <c r="C30" s="3">
         <v>26</v>
       </c>
       <c r="D30" s="7">
         <v>45942</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="3:6" ht="15" customHeight="1">
+    <row r="31" customHeight="1" spans="3:6">
       <c r="C31" s="3">
         <v>27</v>
       </c>
       <c r="D31" s="7">
         <v>45943</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="3:6" ht="15" customHeight="1">
+    <row r="32" customHeight="1" spans="3:6">
       <c r="C32" s="1">
         <v>28</v>
       </c>
@@ -1093,7 +1701,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="15" customHeight="1">
+    <row r="33" customHeight="1" spans="3:6">
       <c r="C33" s="2">
         <v>29</v>
       </c>
@@ -1107,7 +1715,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="15" customHeight="1">
+    <row r="34" customHeight="1" spans="3:6">
       <c r="C34" s="2">
         <v>30</v>
       </c>
@@ -1121,35 +1729,35 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="15" customHeight="1">
+    <row r="35" customHeight="1" spans="3:6">
       <c r="C35" s="3">
         <v>31</v>
       </c>
       <c r="D35" s="7">
         <v>45947</v>
       </c>
-      <c r="E35" s="16" t="s">
+      <c r="E35" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="15" customHeight="1">
+    <row r="36" customHeight="1" spans="3:6">
       <c r="C36" s="6">
         <v>32</v>
       </c>
       <c r="D36" s="8">
         <v>45948</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="19" t="s">
         <v>15</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="15" customHeight="1">
+    <row r="37" customHeight="1" spans="3:6">
       <c r="C37" s="2">
         <v>33</v>
       </c>
@@ -1163,7 +1771,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="15" customHeight="1">
+    <row r="38" customHeight="1" spans="3:6">
       <c r="C38" s="2">
         <v>34</v>
       </c>
@@ -1177,21 +1785,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="15" customHeight="1">
+    <row r="39" customHeight="1" spans="3:6">
       <c r="C39" s="3">
         <v>35</v>
       </c>
       <c r="D39" s="7">
         <v>45951</v>
       </c>
-      <c r="E39" s="16">
+      <c r="E39" s="17">
         <v>5</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="15" customHeight="1">
+    <row r="41" customHeight="1" spans="3:6">
       <c r="C41">
         <v>36</v>
       </c>
@@ -1205,7 +1813,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="15" customHeight="1">
+    <row r="42" customHeight="1" spans="3:6">
       <c r="C42">
         <v>37</v>
       </c>
@@ -1216,91 +1824,91 @@
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="15" customHeight="1">
-      <c r="C44" s="14">
+    <row r="44" customHeight="1" spans="3:6">
+      <c r="C44" s="4">
         <v>38</v>
       </c>
-      <c r="D44" s="14">
+      <c r="D44" s="4">
         <v>25.11</v>
       </c>
-      <c r="E44" s="14">
+      <c r="E44" s="4">
         <v>3</v>
       </c>
-      <c r="F44" s="14"/>
-    </row>
-    <row r="45" spans="3:6" ht="15" customHeight="1">
-      <c r="C45" s="14">
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" customHeight="1" spans="3:6">
+      <c r="C45" s="4">
         <v>39</v>
       </c>
-      <c r="D45" s="14">
+      <c r="D45" s="4">
         <v>28.11</v>
       </c>
-      <c r="E45" s="14">
+      <c r="E45" s="4">
         <v>3</v>
       </c>
-      <c r="F45" s="14"/>
-    </row>
-    <row r="46" spans="3:6" ht="15" customHeight="1">
-      <c r="C46" s="14">
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" customHeight="1" spans="3:6">
+      <c r="C46" s="4">
         <v>40</v>
       </c>
-      <c r="D46" s="14">
+      <c r="D46" s="4">
         <v>29.11</v>
       </c>
-      <c r="E46" s="14">
+      <c r="E46" s="4">
         <v>3</v>
       </c>
-      <c r="F46" s="14"/>
-    </row>
-    <row r="47" spans="3:6" ht="15" customHeight="1">
-      <c r="C47" s="14">
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" customHeight="1" spans="3:6">
+      <c r="C47" s="4">
         <v>41</v>
       </c>
-      <c r="D47" s="14">
+      <c r="D47" s="4">
         <v>30.11</v>
       </c>
-      <c r="E47" s="14">
+      <c r="E47" s="4">
         <v>3</v>
       </c>
-      <c r="F47" s="14" t="s">
+      <c r="F47" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="15" customHeight="1">
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28" t="s">
+    <row r="48" customHeight="1" spans="3:6">
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="F48" s="28"/>
-    </row>
-    <row r="49" spans="3:6" ht="15" customHeight="1">
-      <c r="C49" s="27">
+      <c r="F48" s="14"/>
+    </row>
+    <row r="49" customHeight="1" spans="3:6">
+      <c r="C49" s="4">
         <v>43</v>
       </c>
-      <c r="D49" s="29">
+      <c r="D49" s="5">
         <v>45993</v>
       </c>
-      <c r="E49" s="27">
+      <c r="E49" s="4">
         <v>3</v>
       </c>
-      <c r="F49" s="27" t="s">
+      <c r="F49" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="15" customHeight="1">
-      <c r="C50" s="28"/>
-      <c r="D50" s="28"/>
-      <c r="E50" s="28" t="s">
+    <row r="50" customHeight="1" spans="3:6">
+      <c r="C50" s="14"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="F50" s="28"/>
-    </row>
-    <row r="51" spans="3:6" ht="15" customHeight="1">
+      <c r="F50" s="14"/>
+    </row>
+    <row r="51" customHeight="1" spans="3:6">
       <c r="C51" s="2">
         <v>44</v>
       </c>
-      <c r="D51" s="30">
+      <c r="D51" s="9">
         <v>45995</v>
       </c>
       <c r="E51" s="2">
@@ -1310,50 +1918,65 @@
         <v>62</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="15" customHeight="1">
-      <c r="C52" s="27">
+    <row r="52" customHeight="1" spans="3:6">
+      <c r="C52" s="4">
         <v>45</v>
       </c>
-      <c r="D52" s="29">
+      <c r="D52" s="5">
         <v>46000</v>
       </c>
-      <c r="E52" s="27">
+      <c r="E52" s="4">
         <v>3</v>
       </c>
-      <c r="F52" s="27" t="s">
+      <c r="F52" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="15" customHeight="1">
-      <c r="C53" s="27">
+    <row r="53" customHeight="1" spans="3:6">
+      <c r="C53" s="4">
         <v>46</v>
       </c>
-      <c r="D53" s="29">
+      <c r="D53" s="5">
         <v>46001</v>
       </c>
-      <c r="E53" s="27">
+      <c r="E53" s="4">
         <v>3</v>
       </c>
-      <c r="F53" s="27" t="s">
+      <c r="F53" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="15" customHeight="1">
-      <c r="C54" s="27">
+    <row r="54" customHeight="1" spans="3:6">
+      <c r="C54" s="4">
         <v>47</v>
       </c>
-      <c r="D54" s="29">
+      <c r="D54" s="5">
         <v>46002</v>
       </c>
-      <c r="E54" s="27">
+      <c r="E54" s="4">
         <v>3</v>
       </c>
-      <c r="F54" s="27" t="s">
+      <c r="F54" s="4" t="s">
         <v>65</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:6">
+      <c r="C55" s="15">
+        <v>48</v>
+      </c>
+      <c r="D55" s="15">
+        <v>12.12</v>
+      </c>
+      <c r="E55" s="15">
+        <v>4</v>
+      </c>
+      <c r="F55" s="15" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>